--- a/data/raw/Entropydata.xlsx
+++ b/data/raw/Entropydata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CERI\Carla_16S\shannon_export\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01_Work\02_ActiveProjects\Project_16S_Kruger\Manuscript_analysis\GIT\16S_Kruger_Comparative_Analysis_and_Microbial_Diversity\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CECBB87-86D4-4871-9EA2-97087762FAB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E57A33AC-C371-4BFB-A97D-78057DC35639}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{9DF030D2-8F35-48CB-8D4C-4939DCAABBFC}"/>
+    <workbookView xWindow="300" yWindow="1152" windowWidth="22740" windowHeight="11220" xr2:uid="{9DF030D2-8F35-48CB-8D4C-4939DCAABBFC}"/>
   </bookViews>
   <sheets>
     <sheet name="alpha-diversity" sheetId="2" r:id="rId1"/>
@@ -410,9 +410,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -448,7 +447,7 @@
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_1" connectionId="1" xr16:uid="{0E2F689E-BB40-467D-A9EB-F08554FC43C9}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="9" unboundColumnsRight="2">
+  <queryTableRefresh nextId="11" unboundColumnsRight="2">
     <queryTableFields count="6">
       <queryTableField id="1" name="Column1" tableColumnId="1"/>
       <queryTableField id="4" dataBound="0" tableColumnId="4"/>
@@ -464,6 +463,9 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BE027BDE-5E44-4EC0-A067-26CE54BFE44D}" name="alpha_diversity" displayName="alpha_diversity" ref="A1:F1048576" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:F1048576" xr:uid="{BE027BDE-5E44-4EC0-A067-26CE54BFE44D}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F90">
+    <sortCondition ref="A1:A1048576"/>
+  </sortState>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{E4AE4BF3-1577-4649-A4E1-59B537E10C74}" uniqueName="1" name="Sample_id" queryTableFieldId="1" dataDxfId="4"/>
     <tableColumn id="4" xr3:uid="{E62D680B-FD0F-44BC-93AE-3604D7E726D8}" uniqueName="4" name="Common.name_Species" queryTableFieldId="4" dataDxfId="3"/>
@@ -798,7 +800,6 @@
   <cols>
     <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -834,10 +835,10 @@
       <c r="D2">
         <v>7.0275146597740363</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2">
         <v>18.868582472570498</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F2">
         <v>165</v>
       </c>
     </row>
@@ -854,10 +855,10 @@
       <c r="D3">
         <v>5.8299546404550915</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3">
         <v>7.7397287518277302</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F3">
         <v>68</v>
       </c>
     </row>
@@ -874,10 +875,10 @@
       <c r="D4">
         <v>6.159209797826894</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4">
         <v>9.9351035378431103</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F4">
         <v>90</v>
       </c>
     </row>
@@ -894,10 +895,10 @@
       <c r="D5">
         <v>5.6196076762397409</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5">
         <v>6.54563140950712</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5">
         <v>63</v>
       </c>
     </row>
@@ -914,10 +915,10 @@
       <c r="D6">
         <v>6.1569794775727722</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6">
         <v>9.0187670348239699</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6">
         <v>90</v>
       </c>
     </row>
@@ -934,10 +935,10 @@
       <c r="D7">
         <v>5.9327627027437631</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7">
         <v>8.4780691642965706</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F7">
         <v>80</v>
       </c>
     </row>
@@ -954,10 +955,10 @@
       <c r="D8">
         <v>6.0512518732291571</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8">
         <v>11.8844185704037</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8">
         <v>87</v>
       </c>
     </row>
@@ -974,10 +975,10 @@
       <c r="D9">
         <v>4.9779312941329561</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9">
         <v>5.3116697856024597</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F9">
         <v>40</v>
       </c>
     </row>
@@ -994,10 +995,10 @@
       <c r="D10">
         <v>5.3196292891840251</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10">
         <v>5.3514855188226704</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F10">
         <v>59</v>
       </c>
     </row>
@@ -1014,10 +1015,10 @@
       <c r="D11">
         <v>6.0218644765115474</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11">
         <v>8.8802726886394598</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F11">
         <v>85</v>
       </c>
     </row>
@@ -1034,10 +1035,10 @@
       <c r="D12">
         <v>6.0189154188150082</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12">
         <v>8.9861906831054004</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F12">
         <v>80</v>
       </c>
     </row>
@@ -1046,18 +1047,18 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D13">
         <v>5.6595961962046912</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13">
         <v>8.1443201633902707</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F13">
         <v>64</v>
       </c>
     </row>
@@ -1074,10 +1075,10 @@
       <c r="D14">
         <v>5.3188628725433098</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14">
         <v>5.2292485055192603</v>
       </c>
-      <c r="F14" s="1">
+      <c r="F14">
         <v>45</v>
       </c>
     </row>
@@ -1094,10 +1095,10 @@
       <c r="D15">
         <v>5.6296512609730947</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15">
         <v>6.2997600776313298</v>
       </c>
-      <c r="F15" s="1">
+      <c r="F15">
         <v>59</v>
       </c>
     </row>
@@ -1114,10 +1115,10 @@
       <c r="D16">
         <v>5.6580805216839369</v>
       </c>
-      <c r="E16" s="1">
+      <c r="E16">
         <v>7.1847966333842797</v>
       </c>
-      <c r="F16" s="1">
+      <c r="F16">
         <v>62</v>
       </c>
     </row>
@@ -1134,10 +1135,10 @@
       <c r="D17">
         <v>6.23359627647904</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E17">
         <v>6.8866282968557604</v>
       </c>
-      <c r="F17" s="1">
+      <c r="F17">
         <v>94</v>
       </c>
     </row>
@@ -1154,10 +1155,10 @@
       <c r="D18">
         <v>5.6496742667807966</v>
       </c>
-      <c r="E18" s="1">
+      <c r="E18">
         <v>6.8942993413301501</v>
       </c>
-      <c r="F18" s="1">
+      <c r="F18">
         <v>62</v>
       </c>
     </row>
@@ -1174,10 +1175,10 @@
       <c r="D19">
         <v>5.2747103640788513</v>
       </c>
-      <c r="E19" s="1">
+      <c r="E19">
         <v>5.7684258262565802</v>
       </c>
-      <c r="F19" s="1">
+      <c r="F19">
         <v>51</v>
       </c>
     </row>
@@ -1194,10 +1195,10 @@
       <c r="D20">
         <v>5.5841047034060844</v>
       </c>
-      <c r="E20" s="1">
+      <c r="E20">
         <v>8.6864390204239097</v>
       </c>
-      <c r="F20" s="1">
+      <c r="F20">
         <v>66</v>
       </c>
     </row>
@@ -1214,10 +1215,10 @@
       <c r="D21">
         <v>5.7721946370057866</v>
       </c>
-      <c r="E21" s="1">
+      <c r="E21">
         <v>10.591620524083799</v>
       </c>
-      <c r="F21" s="1">
+      <c r="F21">
         <v>80</v>
       </c>
     </row>
@@ -1234,10 +1235,10 @@
       <c r="D22">
         <v>6.3044727641629059</v>
       </c>
-      <c r="E22" s="1">
+      <c r="E22">
         <v>8.2307454508084703</v>
       </c>
-      <c r="F22" s="1">
+      <c r="F22">
         <v>99</v>
       </c>
     </row>
@@ -1246,7 +1247,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C23" t="s">
         <v>101</v>
@@ -1254,10 +1255,10 @@
       <c r="D23">
         <v>6.9013321857546961</v>
       </c>
-      <c r="E23" s="1">
+      <c r="E23">
         <v>19.673405462521401</v>
       </c>
-      <c r="F23" s="1">
+      <c r="F23">
         <v>157</v>
       </c>
     </row>
@@ -1266,7 +1267,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C24" t="s">
         <v>101</v>
@@ -1274,10 +1275,10 @@
       <c r="D24">
         <v>5.1511008545643033</v>
       </c>
-      <c r="E24" s="1">
+      <c r="E24">
         <v>5.04837253096699</v>
       </c>
-      <c r="F24" s="1">
+      <c r="F24">
         <v>47</v>
       </c>
     </row>
@@ -1294,10 +1295,10 @@
       <c r="D25">
         <v>6.0561414340188211</v>
       </c>
-      <c r="E25" s="1">
+      <c r="E25">
         <v>7.4928561438627499</v>
       </c>
-      <c r="F25" s="1">
+      <c r="F25">
         <v>78</v>
       </c>
     </row>
@@ -1314,10 +1315,10 @@
       <c r="D26">
         <v>5.6009955881269731</v>
       </c>
-      <c r="E26" s="1">
+      <c r="E26">
         <v>7.5891538954041904</v>
       </c>
-      <c r="F26" s="1">
+      <c r="F26">
         <v>80</v>
       </c>
     </row>
@@ -1334,10 +1335,10 @@
       <c r="D27">
         <v>5.6071837713441841</v>
       </c>
-      <c r="E27" s="1">
+      <c r="E27">
         <v>7.2281822499633002</v>
       </c>
-      <c r="F27" s="1">
+      <c r="F27">
         <v>66</v>
       </c>
     </row>
@@ -1354,10 +1355,10 @@
       <c r="D28">
         <v>6.2988459701827466</v>
       </c>
-      <c r="E28" s="1">
+      <c r="E28">
         <v>10.291297443518101</v>
       </c>
-      <c r="F28" s="1">
+      <c r="F28">
         <v>105</v>
       </c>
     </row>
@@ -1374,10 +1375,10 @@
       <c r="D29">
         <v>5.5887995230334591</v>
       </c>
-      <c r="E29" s="1">
+      <c r="E29">
         <v>6.2911649442682496</v>
       </c>
-      <c r="F29" s="1">
+      <c r="F29">
         <v>57</v>
       </c>
     </row>
@@ -1394,10 +1395,10 @@
       <c r="D30">
         <v>6.4575277586312883</v>
       </c>
-      <c r="E30" s="1">
+      <c r="E30">
         <v>11.4421424968748</v>
       </c>
-      <c r="F30" s="1">
+      <c r="F30">
         <v>111</v>
       </c>
     </row>
@@ -1414,10 +1415,10 @@
       <c r="D31">
         <v>5.8956976964212773</v>
       </c>
-      <c r="E31" s="1">
+      <c r="E31">
         <v>8.3129998627785096</v>
       </c>
-      <c r="F31" s="1">
+      <c r="F31">
         <v>83</v>
       </c>
     </row>
@@ -1434,10 +1435,10 @@
       <c r="D32">
         <v>5.9327036486239013</v>
       </c>
-      <c r="E32" s="1">
+      <c r="E32">
         <v>9.1962532348159005</v>
       </c>
-      <c r="F32" s="1">
+      <c r="F32">
         <v>74</v>
       </c>
     </row>
@@ -1446,18 +1447,18 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C33" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D33">
         <v>7.0834702463520882</v>
       </c>
-      <c r="E33" s="1">
+      <c r="E33">
         <v>19.528570732192001</v>
       </c>
-      <c r="F33" s="1">
+      <c r="F33">
         <v>173</v>
       </c>
     </row>
@@ -1466,18 +1467,18 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C34" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D34">
         <v>7.0363271341327698</v>
       </c>
-      <c r="E34" s="1">
+      <c r="E34">
         <v>17.417735549389501</v>
       </c>
-      <c r="F34" s="1">
+      <c r="F34">
         <v>169</v>
       </c>
     </row>
@@ -1494,10 +1495,10 @@
       <c r="D35">
         <v>6.6580505246501307</v>
       </c>
-      <c r="E35" s="1">
+      <c r="E35">
         <v>15.252904498742801</v>
       </c>
-      <c r="F35" s="1">
+      <c r="F35">
         <v>127</v>
       </c>
     </row>
@@ -1514,10 +1515,10 @@
       <c r="D36">
         <v>6.1431203520370863</v>
       </c>
-      <c r="E36" s="1">
+      <c r="E36">
         <v>12.0078226409493</v>
       </c>
-      <c r="F36" s="1">
+      <c r="F36">
         <v>90</v>
       </c>
     </row>
@@ -1534,10 +1535,10 @@
       <c r="D37">
         <v>7.2955408188956925</v>
       </c>
-      <c r="E37" s="1">
+      <c r="E37">
         <v>22.274043244639198</v>
       </c>
-      <c r="F37" s="1">
+      <c r="F37">
         <v>195</v>
       </c>
     </row>
@@ -1554,10 +1555,10 @@
       <c r="D38">
         <v>6.1192838346124807</v>
       </c>
-      <c r="E38" s="1">
+      <c r="E38">
         <v>11.5873279035116</v>
       </c>
-      <c r="F38" s="1">
+      <c r="F38">
         <v>87</v>
       </c>
     </row>
@@ -1574,10 +1575,10 @@
       <c r="D39">
         <v>6.8147104029699763</v>
       </c>
-      <c r="E39" s="1">
+      <c r="E39">
         <v>19.827189587802</v>
       </c>
-      <c r="F39" s="1">
+      <c r="F39">
         <v>160</v>
       </c>
     </row>
@@ -1586,18 +1587,18 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C40" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D40">
         <v>6.8568091317755444</v>
       </c>
-      <c r="E40" s="1">
+      <c r="E40">
         <v>15.165695590288101</v>
       </c>
-      <c r="F40" s="1">
+      <c r="F40">
         <v>150</v>
       </c>
     </row>
@@ -1606,18 +1607,18 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C41" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D41">
         <v>6.8100105911856952</v>
       </c>
-      <c r="E41" s="1">
+      <c r="E41">
         <v>15.1052463900585</v>
       </c>
-      <c r="F41" s="1">
+      <c r="F41">
         <v>143</v>
       </c>
     </row>
@@ -1634,10 +1635,10 @@
       <c r="D42">
         <v>5.5107827692754681</v>
       </c>
-      <c r="E42" s="1">
+      <c r="E42">
         <v>8.8301824216724594</v>
       </c>
-      <c r="F42" s="1">
+      <c r="F42">
         <v>57</v>
       </c>
     </row>
@@ -1654,10 +1655,10 @@
       <c r="D43">
         <v>6.7478531557575216</v>
       </c>
-      <c r="E43" s="1">
+      <c r="E43">
         <v>13.852834454317099</v>
       </c>
-      <c r="F43" s="1">
+      <c r="F43">
         <v>137</v>
       </c>
     </row>
@@ -1674,10 +1675,10 @@
       <c r="D44">
         <v>6.5442682009939448</v>
       </c>
-      <c r="E44" s="1">
+      <c r="E44">
         <v>13.194323208348701</v>
       </c>
-      <c r="F44" s="1">
+      <c r="F44">
         <v>118</v>
       </c>
     </row>
@@ -1694,10 +1695,10 @@
       <c r="D45">
         <v>6.0548429101909091</v>
       </c>
-      <c r="E45" s="1">
+      <c r="E45">
         <v>10.703586982429201</v>
       </c>
-      <c r="F45" s="1">
+      <c r="F45">
         <v>89</v>
       </c>
     </row>
@@ -1714,10 +1715,10 @@
       <c r="D46">
         <v>6.1704156890126756</v>
       </c>
-      <c r="E46" s="1">
+      <c r="E46">
         <v>13.8509902096795</v>
       </c>
-      <c r="F46" s="1">
+      <c r="F46">
         <v>95</v>
       </c>
     </row>
@@ -1734,10 +1735,10 @@
       <c r="D47">
         <v>7.0097419925388307</v>
       </c>
-      <c r="E47" s="1">
+      <c r="E47">
         <v>16.1497513755819</v>
       </c>
-      <c r="F47" s="1">
+      <c r="F47">
         <v>176</v>
       </c>
     </row>
@@ -1746,7 +1747,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C48" t="s">
         <v>102</v>
@@ -1754,10 +1755,10 @@
       <c r="D48">
         <v>5.5435107557376266</v>
       </c>
-      <c r="E48" s="1">
+      <c r="E48">
         <v>10.361427631707301</v>
       </c>
-      <c r="F48" s="1">
+      <c r="F48">
         <v>64</v>
       </c>
     </row>
@@ -1766,7 +1767,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C49" t="s">
         <v>102</v>
@@ -1774,10 +1775,10 @@
       <c r="D49">
         <v>6.5390931895745785</v>
       </c>
-      <c r="E49" s="1">
+      <c r="E49">
         <v>14.1757258890432</v>
       </c>
-      <c r="F49" s="1">
+      <c r="F49">
         <v>119</v>
       </c>
     </row>
@@ -1794,10 +1795,10 @@
       <c r="D50">
         <v>6.6724573443510948</v>
       </c>
-      <c r="E50" s="1">
+      <c r="E50">
         <v>13.957607701139301</v>
       </c>
-      <c r="F50" s="1">
+      <c r="F50">
         <v>139</v>
       </c>
     </row>
@@ -1814,10 +1815,10 @@
       <c r="D51">
         <v>7.4586873131348481</v>
       </c>
-      <c r="E51" s="1">
+      <c r="E51">
         <v>22.1568937499169</v>
       </c>
-      <c r="F51" s="1">
+      <c r="F51">
         <v>222</v>
       </c>
     </row>
@@ -1834,10 +1835,10 @@
       <c r="D52">
         <v>6.7840953826254236</v>
       </c>
-      <c r="E52" s="1">
+      <c r="E52">
         <v>16.029200143583999</v>
       </c>
-      <c r="F52" s="1">
+      <c r="F52">
         <v>147</v>
       </c>
     </row>
@@ -1854,10 +1855,10 @@
       <c r="D53">
         <v>6.1548196421560597</v>
       </c>
-      <c r="E53" s="1">
+      <c r="E53">
         <v>12.702198745634</v>
       </c>
-      <c r="F53" s="1">
+      <c r="F53">
         <v>99</v>
       </c>
     </row>
@@ -1874,10 +1875,10 @@
       <c r="D54">
         <v>7.1097411797657815</v>
       </c>
-      <c r="E54" s="1">
+      <c r="E54">
         <v>18.301744908748699</v>
       </c>
-      <c r="F54" s="1">
+      <c r="F54">
         <v>186</v>
       </c>
     </row>
@@ -1894,10 +1895,10 @@
       <c r="D55">
         <v>5.6092489270501922</v>
       </c>
-      <c r="E55" s="1">
+      <c r="E55">
         <v>7.3467221182353697</v>
       </c>
-      <c r="F55" s="1">
+      <c r="F55">
         <v>58</v>
       </c>
     </row>
@@ -1914,10 +1915,10 @@
       <c r="D56">
         <v>5.627346098993331</v>
       </c>
-      <c r="E56" s="1">
+      <c r="E56">
         <v>9.7314328476641396</v>
       </c>
-      <c r="F56" s="1">
+      <c r="F56">
         <v>64</v>
       </c>
     </row>
@@ -1934,10 +1935,10 @@
       <c r="D57">
         <v>5.4679753823795769</v>
       </c>
-      <c r="E57" s="1">
+      <c r="E57">
         <v>10.350692723016</v>
       </c>
-      <c r="F57" s="1">
+      <c r="F57">
         <v>62</v>
       </c>
     </row>
@@ -1954,10 +1955,10 @@
       <c r="D58">
         <v>6.9058526934685576</v>
       </c>
-      <c r="E58" s="1">
+      <c r="E58">
         <v>14.4245787765336</v>
       </c>
-      <c r="F58" s="1">
+      <c r="F58">
         <v>146</v>
       </c>
     </row>
@@ -1974,10 +1975,10 @@
       <c r="D59">
         <v>6.1858472740810573</v>
       </c>
-      <c r="E59" s="1">
+      <c r="E59">
         <v>13.8808545865173</v>
       </c>
-      <c r="F59" s="1">
+      <c r="F59">
         <v>93</v>
       </c>
     </row>
@@ -1994,10 +1995,10 @@
       <c r="D60">
         <v>4.6626050979346196</v>
       </c>
-      <c r="E60" s="1">
+      <c r="E60">
         <v>7.9078028020435998</v>
       </c>
-      <c r="F60" s="1">
+      <c r="F60">
         <v>41</v>
       </c>
     </row>
@@ -2006,18 +2007,18 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C61" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D61">
         <v>6.9414066098927094</v>
       </c>
-      <c r="E61" s="1">
+      <c r="E61">
         <v>20.428772628773199</v>
       </c>
-      <c r="F61" s="1">
+      <c r="F61">
         <v>155</v>
       </c>
     </row>
@@ -2026,18 +2027,18 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C62" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D62">
         <v>6.8920446133338151</v>
       </c>
-      <c r="E62" s="1">
+      <c r="E62">
         <v>20.324725402602802</v>
       </c>
-      <c r="F62" s="1">
+      <c r="F62">
         <v>157</v>
       </c>
     </row>
@@ -2054,10 +2055,10 @@
       <c r="D63">
         <v>6.8872394818655547</v>
       </c>
-      <c r="E63" s="1">
+      <c r="E63">
         <v>21.3056575471462</v>
       </c>
-      <c r="F63" s="1">
+      <c r="F63">
         <v>156</v>
       </c>
     </row>
@@ -2074,10 +2075,10 @@
       <c r="D64">
         <v>7.3397197997281038</v>
       </c>
-      <c r="E64" s="1">
+      <c r="E64">
         <v>20.515879123397401</v>
       </c>
-      <c r="F64" s="1">
+      <c r="F64">
         <v>199</v>
       </c>
     </row>
@@ -2094,10 +2095,10 @@
       <c r="D65">
         <v>7.0802409616299968</v>
       </c>
-      <c r="E65" s="1">
+      <c r="E65">
         <v>17.8715798570882</v>
       </c>
-      <c r="F65" s="1">
+      <c r="F65">
         <v>167</v>
       </c>
     </row>
@@ -2114,10 +2115,10 @@
       <c r="D66">
         <v>6.2583886790908494</v>
       </c>
-      <c r="E66" s="1">
+      <c r="E66">
         <v>15.074198109432899</v>
       </c>
-      <c r="F66" s="1">
+      <c r="F66">
         <v>101</v>
       </c>
     </row>
@@ -2134,10 +2135,10 @@
       <c r="D67">
         <v>6.0023985514330107</v>
       </c>
-      <c r="E67" s="1">
+      <c r="E67">
         <v>14.157818633760501</v>
       </c>
-      <c r="F67" s="1">
+      <c r="F67">
         <v>85</v>
       </c>
     </row>
@@ -2154,10 +2155,10 @@
       <c r="D68">
         <v>7.0205275264861964</v>
       </c>
-      <c r="E68" s="1">
+      <c r="E68">
         <v>21.6199082880491</v>
       </c>
-      <c r="F68" s="1">
+      <c r="F68">
         <v>169</v>
       </c>
     </row>
@@ -2174,10 +2175,10 @@
       <c r="D69">
         <v>6.7529015752894095</v>
       </c>
-      <c r="E69" s="1">
+      <c r="E69">
         <v>16.379001786817302</v>
       </c>
-      <c r="F69" s="1">
+      <c r="F69">
         <v>137</v>
       </c>
     </row>
@@ -2186,7 +2187,7 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C70" t="s">
         <v>103</v>
@@ -2194,10 +2195,10 @@
       <c r="D70">
         <v>6.9342732214808036</v>
       </c>
-      <c r="E70" s="1">
+      <c r="E70">
         <v>20.7289680091477</v>
       </c>
-      <c r="F70" s="1">
+      <c r="F70">
         <v>157</v>
       </c>
     </row>
@@ -2206,7 +2207,7 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C71" t="s">
         <v>103</v>
@@ -2214,10 +2215,10 @@
       <c r="D71">
         <v>7.6974446454861258</v>
       </c>
-      <c r="E71" s="1">
+      <c r="E71">
         <v>22.895468813373402</v>
       </c>
-      <c r="F71" s="1">
+      <c r="F71">
         <v>259</v>
       </c>
     </row>
@@ -2226,7 +2227,7 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C72" t="s">
         <v>103</v>
@@ -2234,10 +2235,10 @@
       <c r="D72">
         <v>6.5199649803261508</v>
       </c>
-      <c r="E72" s="1">
+      <c r="E72">
         <v>15.3973955559301</v>
       </c>
-      <c r="F72" s="1">
+      <c r="F72">
         <v>110</v>
       </c>
     </row>
@@ -2254,10 +2255,10 @@
       <c r="D73">
         <v>7.5418893669370357</v>
       </c>
-      <c r="E73" s="1">
+      <c r="E73">
         <v>23.485192443197601</v>
       </c>
-      <c r="F73" s="1">
+      <c r="F73">
         <v>230</v>
       </c>
     </row>
@@ -2274,10 +2275,10 @@
       <c r="D74">
         <v>5.8795411093607584</v>
       </c>
-      <c r="E74" s="1">
+      <c r="E74">
         <v>12.5053834928034</v>
       </c>
-      <c r="F74" s="1">
+      <c r="F74">
         <v>72</v>
       </c>
     </row>
@@ -2294,10 +2295,10 @@
       <c r="D75">
         <v>6.8100949110542857</v>
       </c>
-      <c r="E75" s="1">
+      <c r="E75">
         <v>18.434799489101</v>
       </c>
-      <c r="F75" s="1">
+      <c r="F75">
         <v>144</v>
       </c>
     </row>
@@ -2314,10 +2315,10 @@
       <c r="D76">
         <v>6.5264057602888377</v>
       </c>
-      <c r="E76" s="1">
+      <c r="E76">
         <v>14.046261801062901</v>
       </c>
-      <c r="F76" s="1">
+      <c r="F76">
         <v>115</v>
       </c>
     </row>
@@ -2334,10 +2335,10 @@
       <c r="D77">
         <v>7.5192754571777165</v>
       </c>
-      <c r="E77" s="1">
+      <c r="E77">
         <v>21.7101787249909</v>
       </c>
-      <c r="F77" s="1">
+      <c r="F77">
         <v>231</v>
       </c>
     </row>
@@ -2346,7 +2347,7 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C78" t="s">
         <v>103</v>
@@ -2354,10 +2355,10 @@
       <c r="D78">
         <v>6.2601834671082326</v>
       </c>
-      <c r="E78" s="1">
+      <c r="E78">
         <v>14.3256123434389</v>
       </c>
-      <c r="F78" s="1">
+      <c r="F78">
         <v>97</v>
       </c>
     </row>
@@ -2366,7 +2367,7 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C79" t="s">
         <v>103</v>
@@ -2374,10 +2375,10 @@
       <c r="D79">
         <v>7.1405483090304616</v>
       </c>
-      <c r="E79" s="1">
+      <c r="E79">
         <v>18.472882965142301</v>
       </c>
-      <c r="F79" s="1">
+      <c r="F79">
         <v>174</v>
       </c>
     </row>
@@ -2386,7 +2387,7 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C80" t="s">
         <v>103</v>
@@ -2394,10 +2395,10 @@
       <c r="D80">
         <v>6.742217723090894</v>
       </c>
-      <c r="E80" s="1">
+      <c r="E80">
         <v>17.565855197286101</v>
       </c>
-      <c r="F80" s="1">
+      <c r="F80">
         <v>144</v>
       </c>
     </row>
@@ -2406,7 +2407,7 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C81" t="s">
         <v>103</v>
@@ -2414,10 +2415,10 @@
       <c r="D81">
         <v>5.9453847777092088</v>
       </c>
-      <c r="E81" s="1">
+      <c r="E81">
         <v>8.9754913076295306</v>
       </c>
-      <c r="F81" s="1">
+      <c r="F81">
         <v>86</v>
       </c>
     </row>
@@ -2434,10 +2435,10 @@
       <c r="D82">
         <v>7.1351764995684945</v>
       </c>
-      <c r="E82" s="1">
+      <c r="E82">
         <v>21.227554160529198</v>
       </c>
-      <c r="F82" s="1">
+      <c r="F82">
         <v>179</v>
       </c>
     </row>
@@ -2454,10 +2455,10 @@
       <c r="D83">
         <v>6.7312903301485303</v>
       </c>
-      <c r="E83" s="1">
+      <c r="E83">
         <v>16.539976525658499</v>
       </c>
-      <c r="F83" s="1">
+      <c r="F83">
         <v>135</v>
       </c>
     </row>
@@ -2474,10 +2475,10 @@
       <c r="D84">
         <v>7.223779260936543</v>
       </c>
-      <c r="E84" s="1">
+      <c r="E84">
         <v>18.2501325013233</v>
       </c>
-      <c r="F84" s="1">
+      <c r="F84">
         <v>184</v>
       </c>
     </row>
@@ -2494,10 +2495,10 @@
       <c r="D85">
         <v>6.6361264442182142</v>
       </c>
-      <c r="E85" s="1">
+      <c r="E85">
         <v>16.8875278777818</v>
       </c>
-      <c r="F85" s="1">
+      <c r="F85">
         <v>127</v>
       </c>
     </row>
@@ -2514,10 +2515,10 @@
       <c r="D86">
         <v>6.933898447638426</v>
       </c>
-      <c r="E86" s="1">
+      <c r="E86">
         <v>18.0246365011031</v>
       </c>
-      <c r="F86" s="1">
+      <c r="F86">
         <v>156</v>
       </c>
     </row>
@@ -2534,10 +2535,10 @@
       <c r="D87">
         <v>6.9863071009888431</v>
       </c>
-      <c r="E87" s="1">
+      <c r="E87">
         <v>18.4949688878309</v>
       </c>
-      <c r="F87" s="1">
+      <c r="F87">
         <v>167</v>
       </c>
     </row>
@@ -2554,10 +2555,10 @@
       <c r="D88">
         <v>6.7435953013515144</v>
       </c>
-      <c r="E88" s="1">
+      <c r="E88">
         <v>15.442413361009899</v>
       </c>
-      <c r="F88" s="1">
+      <c r="F88">
         <v>138</v>
       </c>
     </row>
@@ -2574,10 +2575,10 @@
       <c r="D89">
         <v>7.0052184146430552</v>
       </c>
-      <c r="E89" s="1">
+      <c r="E89">
         <v>19.378828050968</v>
       </c>
-      <c r="F89" s="1">
+      <c r="F89">
         <v>162</v>
       </c>
     </row>
@@ -2594,10 +2595,10 @@
       <c r="D90">
         <v>5.7452601264179526</v>
       </c>
-      <c r="E90" s="1">
+      <c r="E90">
         <v>11.1528145266444</v>
       </c>
-      <c r="F90" s="1">
+      <c r="F90">
         <v>66</v>
       </c>
     </row>
